--- a/docs/d/203/inyear.xlsx
+++ b/docs/d/203/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 81 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 80 clubs short</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="P13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="9" t="n">
         <v>1</v>
@@ -4663,7 +4663,7 @@
         <v>0</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" s="9" t="n">
         <v>0</v>
@@ -12379,7 +12379,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12423,7 +12423,7 @@
         <v>1</v>
       </c>
       <c r="Q121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
@@ -12434,8 +12434,8 @@
       <c r="T121" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U121" s="9" t="n">
-        <v>0</v>
+      <c r="U121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V121" s="9" t="n">
         <v>0</v>
@@ -14804,7 +14804,7 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -14874,8 +14874,8 @@
       <c r="Y146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z146" s="9" t="n">
-        <v>0</v>
+      <c r="Z146" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA146" s="10" t="n">
         <v>1</v>
@@ -16795,7 +16795,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -16960,7 +16960,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>

--- a/docs/d/203/inyear.xlsx
+++ b/docs/d/203/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/203/inyear.xlsx
+++ b/docs/d/203/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 80 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 74 clubs short</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" s="10" t="n">
         <v>1</v>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2749,8 +2749,8 @@
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="P24" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q24" s="10" t="n">
         <v>2</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3525,8 +3525,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3719,8 +3719,8 @@
       <c r="Y31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="9" t="n">
-        <v>0</v>
+      <c r="Z31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>1</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3816,8 +3816,8 @@
       <c r="Y32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z32" s="9" t="n">
-        <v>0</v>
+      <c r="Z32" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA32" s="10" t="n">
         <v>1</v>
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -8860,8 +8860,8 @@
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10509,8 +10509,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12228,8 +12228,8 @@
       <c r="P119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" s="9" t="n">
-        <v>1</v>
+      <c r="Q119" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R119" s="9" t="n">
         <v>0</v>
@@ -16168,7 +16168,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -16201,7 +16201,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -16234,7 +16234,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16531,7 +16531,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16663,7 +16663,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -16762,7 +16762,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>

--- a/docs/d/203/inyear.xlsx
+++ b/docs/d/203/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 74 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 50 clubs short</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1585,8 +1585,8 @@
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1682,8 +1682,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="10" t="n">
         <v>1</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2361,8 +2361,8 @@
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2458,8 +2458,8 @@
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="9" t="n">
-        <v>0</v>
+      <c r="Z18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="P26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="9" t="n">
         <v>0</v>
@@ -3234,8 +3234,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="9" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4107,8 +4107,8 @@
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA35" s="10" t="n">
         <v>1</v>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4592,8 +4592,8 @@
       <c r="Y40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" s="9" t="n">
-        <v>0</v>
+      <c r="Z40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA40" s="10" t="n">
         <v>1</v>
@@ -4669,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" s="9" t="n">
         <v>0</v>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -4883,8 +4883,8 @@
       <c r="Y43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="9" t="n">
-        <v>0</v>
+      <c r="Z43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA43" s="10" t="n">
         <v>1</v>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5465,8 +5465,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -5562,8 +5562,8 @@
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6532,8 +6532,8 @@
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
@@ -6609,7 +6609,7 @@
         <v>0</v>
       </c>
       <c r="S61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" s="9" t="n">
         <v>0</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6823,8 +6823,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -7793,8 +7793,8 @@
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9151,8 +9151,8 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="P88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q88" s="9" t="n">
         <v>0</v>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10024,8 +10024,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10286,10 +10286,10 @@
         </is>
       </c>
       <c r="P99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R99" s="9" t="n">
         <v>0</v>
@@ -11556,7 +11556,7 @@
         <v>0</v>
       </c>
       <c r="S112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T112" s="9" t="n">
         <v>0</v>
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12061,8 +12061,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12837,8 +12837,8 @@
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="9" t="n">
-        <v>0</v>
+      <c r="Z125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -12961,7 +12961,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13031,8 +13031,8 @@
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="9" t="n">
-        <v>0</v>
+      <c r="Z127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
@@ -13252,7 +13252,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13322,8 +13322,8 @@
       <c r="Y130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z130" s="9" t="n">
-        <v>0</v>
+      <c r="Z130" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA130" s="10" t="n">
         <v>1</v>
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13613,8 +13613,8 @@
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="9" t="n">
-        <v>0</v>
+      <c r="Z133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA133" s="10" t="n">
         <v>1</v>
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14071,8 +14071,8 @@
       <c r="P138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" s="9" t="n">
-        <v>1</v>
+      <c r="Q138" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R138" s="9" t="n">
         <v>0</v>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14195,8 +14195,8 @@
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -14222,7 +14222,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14292,8 +14292,8 @@
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="9" t="n">
-        <v>0</v>
+      <c r="Z140" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA140" s="10" t="n">
         <v>1</v>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14389,8 +14389,8 @@
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -15386,7 +15386,7 @@
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -15456,8 +15456,8 @@
       <c r="Y152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z152" s="9" t="n">
-        <v>0</v>
+      <c r="Z152" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA152" s="10" t="n">
         <v>1</v>
@@ -15912,7 +15912,7 @@
         </is>
       </c>
       <c r="P157" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q157" s="9" t="n">
         <v>0</v>
@@ -16069,7 +16069,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -16135,7 +16135,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16234,7 +16234,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16267,7 +16267,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -16300,7 +16300,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16333,7 +16333,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16399,7 +16399,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16465,7 +16465,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16564,7 +16564,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16630,7 +16630,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16762,7 +16762,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -16828,7 +16828,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -16861,7 +16861,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -16894,7 +16894,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -16927,7 +16927,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -16993,7 +16993,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>

--- a/docs/d/203/inyear.xlsx
+++ b/docs/d/203/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 50 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 50 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1141,17 +1141,17 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M5" s="8" t="n">
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1723,17 +1723,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="8" t="n">
@@ -1752,14 +1752,14 @@
       <c r="P11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="9" t="n">
-        <v>1</v>
+      <c r="Q11" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" s="9" t="n">
         <v>0</v>
@@ -1820,17 +1820,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2014,17 +2014,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M14" s="8" t="n">
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2346,11 +2346,11 @@
       <c r="T17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U17" s="9" t="n">
-        <v>0</v>
+      <c r="U17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2402,17 +2402,17 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M18" s="8" t="n">
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2737,8 +2737,8 @@
       <c r="U21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="9" t="n">
-        <v>3</v>
+      <c r="V21" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>5</v>
@@ -3081,17 +3081,17 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M25" s="8" t="n">
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3372,17 +3372,17 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M28" s="8" t="n">
@@ -3469,17 +3469,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -3517,7 +3517,7 @@
         <v>4</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X29" s="10" t="n">
         <v>6</v>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>1</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" s="9" t="n">
         <v>0</v>
@@ -4286,11 +4286,11 @@
       <c r="T37" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U37" s="9" t="n">
-        <v>0</v>
+      <c r="U37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4439,17 +4439,17 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M39" s="8" t="n">
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -4827,17 +4827,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-18</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M43" s="8" t="n">
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>0</v>
       </c>
       <c r="S44" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T44" s="9" t="n">
         <v>0</v>
@@ -4968,11 +4968,11 @@
       <c r="U44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V44" s="9" t="n">
-        <v>3</v>
+      <c r="V44" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" s="10" t="n">
         <v>6</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5118,17 +5118,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M46" s="8" t="n">
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5215,17 +5215,17 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M47" s="8" t="n">
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5603,17 +5603,17 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M51" s="8" t="n">
@@ -5648,7 +5648,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -5894,17 +5894,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
@@ -5991,17 +5991,17 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M55" s="8" t="n">
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6282,17 +6282,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="8" t="n">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6670,17 +6670,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="8" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -6893,8 +6893,8 @@
       <c r="P64" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q64" s="9" t="n">
-        <v>1</v>
+      <c r="Q64" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R64" s="9" t="n">
         <v>0</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         </is>
       </c>
       <c r="P67" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q67" s="9" t="n">
         <v>0</v>
@@ -7199,8 +7199,8 @@
       <c r="U67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="9" t="n">
-        <v>2</v>
+      <c r="V67" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8319,13 +8319,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -8998,17 +8998,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M86" s="8" t="n">
@@ -9043,7 +9043,7 @@
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9133,14 +9133,14 @@
       <c r="S87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T87" s="9" t="n">
-        <v>0</v>
+      <c r="T87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9192,17 +9192,17 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M88" s="8" t="n">
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -9580,17 +9580,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>0</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11520,17 +11520,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M112" s="8" t="n">
@@ -11549,8 +11549,8 @@
       <c r="P112" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q112" s="9" t="n">
-        <v>0</v>
+      <c r="Q112" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
@@ -11568,7 +11568,7 @@
         <v>4</v>
       </c>
       <c r="W112" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X112" s="10" t="n">
         <v>7</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12102,17 +12102,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12244,7 +12244,7 @@
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
@@ -12296,17 +12296,17 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L120" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M120" s="8" t="n">
@@ -12323,7 +12323,7 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q120" s="9" t="n">
         <v>0</v>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13099,7 +13099,7 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q128" s="9" t="n">
         <v>1</v>
@@ -13169,17 +13169,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L129" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M129" s="8" t="n">
@@ -13211,13 +13211,13 @@
         <v>1</v>
       </c>
       <c r="U129" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V129" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X129" s="10" t="n">
         <v>7</v>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>4</v>
       </c>
       <c r="W131" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X131" s="10" t="n">
         <v>7</v>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>0</v>
       </c>
       <c r="V133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q136" s="9" t="n">
         <v>0</v>
@@ -13896,7 +13896,7 @@
         <v>4</v>
       </c>
       <c r="W136" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X136" s="10" t="n">
         <v>7</v>
@@ -13945,17 +13945,17 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L137" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M137" s="8" t="n">
@@ -14042,13 +14042,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
@@ -14139,13 +14139,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -14222,7 +14222,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14274,8 +14274,8 @@
       <c r="S140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T140" s="9" t="n">
-        <v>0</v>
+      <c r="T140" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U140" s="9" t="n">
         <v>0</v>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>4</v>
       </c>
       <c r="W142" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X142" s="10" t="n">
         <v>7</v>
@@ -14527,17 +14527,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-25</v>
+      </c>
+      <c r="L143" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M143" s="8" t="n">
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -14818,17 +14818,17 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L146" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L146" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M146" s="8" t="n">
@@ -14863,7 +14863,7 @@
         <v>0</v>
       </c>
       <c r="V146" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W146" s="9" t="n">
         <v>0</v>
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -15012,13 +15012,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -15109,13 +15109,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>4</v>
       </c>
       <c r="W149" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X149" s="10" t="n">
         <v>6</v>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>4</v>
       </c>
       <c r="W150" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X150" s="10" t="n">
         <v>4</v>
@@ -15303,13 +15303,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>0</v>
       </c>
       <c r="V152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W152" s="9" t="n">
         <v>0</v>
@@ -15497,13 +15497,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -15594,13 +15594,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L154" s="7" t="inlineStr">
         <is>
@@ -15691,13 +15691,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
@@ -15788,13 +15788,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -15885,13 +15885,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -16069,7 +16069,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -16084,7 +16084,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -16117,7 +16117,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -16135,7 +16135,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16150,7 +16150,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -16168,7 +16168,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -16183,7 +16183,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -16216,7 +16216,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -16234,7 +16234,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16282,7 +16282,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -16300,7 +16300,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16315,7 +16315,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -16348,7 +16348,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -16381,7 +16381,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -16399,7 +16399,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16414,7 +16414,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -16432,7 +16432,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16564,7 +16564,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16579,7 +16579,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -16612,7 +16612,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -16729,7 +16729,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -16744,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -16777,7 +16777,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -16810,7 +16810,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -16876,7 +16876,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -16909,7 +16909,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -16927,7 +16927,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -16975,7 +16975,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">

--- a/docs/d/203/inyear.xlsx
+++ b/docs/d/203/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/203/inyear.xlsx
+++ b/docs/d/203/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/203/inyear.xlsx
+++ b/docs/d/203/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/203/inyear.xlsx
+++ b/docs/d/203/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/203/inyear.xlsx
+++ b/docs/d/203/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 50 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 50 clubs short</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" s="9" t="n">
         <v>0</v>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1664,8 +1664,8 @@
       <c r="S10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T10" s="9" t="n">
-        <v>0</v>
+      <c r="T10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U10" s="9" t="n">
         <v>0</v>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3031,8 +3031,8 @@
       <c r="V24" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W24" s="9" t="n">
-        <v>3</v>
+      <c r="W24" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>5</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3469,17 +3469,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>0</v>
@@ -3516,8 +3516,8 @@
       <c r="V29" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W29" s="9" t="n">
-        <v>3</v>
+      <c r="W29" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X29" s="10" t="n">
         <v>6</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="P30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="9" t="n">
         <v>0</v>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5162,8 +5162,8 @@
       <c r="U46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="9" t="n">
-        <v>3</v>
+      <c r="V46" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -5744,8 +5744,8 @@
       <c r="U52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V52" s="9" t="n">
-        <v>2</v>
+      <c r="V52" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -5894,17 +5894,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L54" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -6891,16 +6891,16 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q64" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="S64" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T64" s="10" t="n">
         <v>1</v>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>1</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10191,8 +10191,8 @@
       <c r="P98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" s="9" t="n">
-        <v>0</v>
+      <c r="Q98" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R98" s="9" t="n">
         <v>0</v>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11700,7 +11700,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -11741,10 +11741,10 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q114" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q114" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R114" s="9" t="n">
         <v>0</v>
@@ -12138,7 +12138,7 @@
         <v>0</v>
       </c>
       <c r="S118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T118" s="9" t="n">
         <v>0</v>
@@ -12323,7 +12323,7 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q120" s="9" t="n">
         <v>0</v>
@@ -12379,7 +12379,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12422,8 +12422,8 @@
       <c r="P121" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q121" s="9" t="n">
-        <v>1</v>
+      <c r="Q121" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="P122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q122" s="9" t="n">
         <v>0</v>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>4</v>
       </c>
       <c r="W131" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X131" s="10" t="n">
         <v>7</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13792,8 +13792,8 @@
       <c r="T135" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U135" s="9" t="n">
-        <v>0</v>
+      <c r="U135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V135" s="9" t="n">
         <v>0</v>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>4</v>
       </c>
       <c r="W136" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X136" s="10" t="n">
         <v>7</v>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>0</v>
       </c>
       <c r="V137" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W137" s="9" t="n">
         <v>0</v>
@@ -14460,13 +14460,13 @@
         <v>0</v>
       </c>
       <c r="Q142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R142" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T142" s="10" t="n">
         <v>1</v>
@@ -15109,13 +15109,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>4</v>
       </c>
       <c r="W149" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X149" s="10" t="n">
         <v>6</v>
@@ -15192,7 +15192,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -15247,8 +15247,8 @@
       <c r="T150" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U150" s="9" t="n">
-        <v>0</v>
+      <c r="U150" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V150" s="10" t="n">
         <v>4</v>
@@ -16069,7 +16069,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -16168,7 +16168,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -16201,7 +16201,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -16216,7 +16216,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -16300,7 +16300,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16333,7 +16333,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -16399,7 +16399,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16630,7 +16630,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16729,7 +16729,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -16795,7 +16795,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -16894,7 +16894,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -16993,7 +16993,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>

--- a/docs/d/203/inyear.xlsx
+++ b/docs/d/203/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:49 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 50 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 50 clubs short</t>
         </is>
       </c>
     </row>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2055,8 +2055,8 @@
       <c r="T14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U14" s="9" t="n">
-        <v>0</v>
+      <c r="U14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V14" s="9" t="n">
         <v>2</v>
@@ -2347,7 +2347,7 @@
         <v>1</v>
       </c>
       <c r="U17" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V17" s="9" t="n">
         <v>2</v>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>4</v>
       </c>
       <c r="W24" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>5</v>
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>4</v>
       </c>
       <c r="W29" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X29" s="10" t="n">
         <v>6</v>
@@ -3957,10 +3957,10 @@
         <v>11</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
@@ -5941,8 +5941,8 @@
       <c r="V54" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W54" s="9" t="n">
-        <v>3</v>
+      <c r="W54" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X54" s="10" t="n">
         <v>5</v>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6611,8 +6611,8 @@
       <c r="S61" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T61" s="9" t="n">
-        <v>0</v>
+      <c r="T61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U61" s="9" t="n">
         <v>0</v>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -6896,8 +6896,8 @@
       <c r="Q64" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R64" s="9" t="n">
-        <v>1</v>
+      <c r="R64" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S64" s="10" t="n">
         <v>2</v>
@@ -6909,7 +6909,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7584,8 +7584,8 @@
       <c r="T71" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U71" s="9" t="n">
-        <v>0</v>
+      <c r="U71" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V71" s="9" t="n">
         <v>1</v>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8069,8 +8069,8 @@
       <c r="T76" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U76" s="9" t="n">
-        <v>0</v>
+      <c r="U76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V76" s="9" t="n">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>0</v>
       </c>
       <c r="S106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T106" s="9" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11267,11 +11267,11 @@
       <c r="S109" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U109" s="9" t="n">
-        <v>0</v>
+      <c r="T109" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U109" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V109" s="9" t="n">
         <v>1</v>
@@ -11426,10 +11426,10 @@
         <v>9</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K136" s="4" t="n">
         <v>-2</v>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16333,7 +16333,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16399,13 +16399,13 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -16465,7 +16465,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16498,7 +16498,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
